--- a/artfynd/A 26500-2026 artfynd.xlsx
+++ b/artfynd/A 26500-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>359231</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661010.0157808348</v>
+        <v>661010</v>
       </c>
       <c r="R2" t="n">
-        <v>7175353.653482229</v>
+        <v>7175354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -788,6 +773,437 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1978086</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SO Umgransele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>661318</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7175415</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-09-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-09-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>59822752</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djuptjärnberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>661023</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7175262</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119536665</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kronoborg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>661175</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7175661</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119536099</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kronoborg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>661230</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7175643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26500-2026 artfynd.xlsx
+++ b/artfynd/A 26500-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1978086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119536665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119536099</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>